--- a/docs/輸入法配置清單.xlsx
+++ b/docs/輸入法配置清單.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C238464-5754-4C02-8ADB-DF7A72A74C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F75B1A3-CFB0-4604-8DF1-E28B728A914C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-195" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{9802FFAC-390A-44F2-8F8B-58A7403FAC33}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9802FFAC-390A-44F2-8F8B-58A7403FAC33}"/>
   </bookViews>
   <sheets>
     <sheet name="輸入方案套件包" sheetId="1" r:id="rId1"/>
-    <sheet name="輸入法建構項目配置表" sheetId="2" r:id="rId2"/>
+    <sheet name="輸入方案套件包 (2)" sheetId="3" r:id="rId2"/>
+    <sheet name="輸入法建構項目配置表" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="65">
   <si>
     <t>tlpa_phing_im.schema.yaml</t>
   </si>
@@ -207,6 +208,64 @@
     <t>rime-tlpa-tlpa-v0.1.zip
 台語拼音（TLPA）</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反切輸入法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tlpa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bpm2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>tps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phing_im_bp.schema.yaml</t>
+  </si>
+  <si>
+    <t>phing_im_bpm2.schema.yaml</t>
+  </si>
+  <si>
+    <t>phing_im_poj.schema.yaml</t>
+  </si>
+  <si>
+    <t>phing_im_tl.schema.yaml</t>
+  </si>
+  <si>
+    <t>phing_im_tlpa.schema.yaml</t>
+  </si>
+  <si>
+    <t>zu_im_bpm2.schema.yaml</t>
+  </si>
+  <si>
+    <t>zu_im_tlpa.schema.yaml</t>
+  </si>
+  <si>
+    <t>huan_ciat_tlpa.schema.yaml</t>
+  </si>
+  <si>
+    <t>huan_ciat_tps.schema.yaml</t>
   </si>
 </sst>
 </file>
@@ -801,6 +860,166 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B26CC07D-EB19-4537-9F1C-9C29C6B6C0EA}">
+  <dimension ref="B2:G11"/>
+  <sheetFormatPr defaultRowHeight="25.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="52.875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="17.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="9"/>
+      <c r="G3" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="19"/>
+      <c r="C4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="11"/>
+      <c r="G4" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="19"/>
+      <c r="C5" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="G5" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="19"/>
+      <c r="C6" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="11"/>
+      <c r="G6" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="20"/>
+      <c r="C7" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="G7" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="22"/>
+      <c r="C9" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="G10" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="22"/>
+      <c r="C11" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AE3C413-E2A6-4475-A1A5-A8D5FE309A7B}">
   <dimension ref="B2:E20"/>
   <sheetFormatPr defaultRowHeight="25.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -998,7 +1217,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1464C311-78E7-4BF2-ABF8-1949D9E4AC35}">
   <dimension ref="B2:E9"/>
   <sheetFormatPr defaultRowHeight="25.5" x14ac:dyDescent="0.25"/>
